--- a/results/Int All Data 0.4/Rando_3_permute.xlsx
+++ b/results/Int All Data 0.4/Rando_3_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9469909078603014</v>
+        <v>0.9412507896399243</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9469909078603014</v>
+        <v>0.9374605180037903</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9469909078603014</v>
+        <v>0.9371446620341124</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9457274839815901</v>
+        <v>0.936197094125079</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9426783458171646</v>
+        <v>0.936197094125079</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9445187708690552</v>
+        <v>0.936197094125079</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9433100577565201</v>
+        <v>0.9384080859128238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9433100577565201</v>
+        <v>0.9384204945402039</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9379529148993773</v>
+        <v>0.9381046385705262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9385299160725566</v>
+        <v>0.9393680624492374</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9350131982673044</v>
+        <v>0.9379952170381735</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9350131982673044</v>
+        <v>0.9364159371897843</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9301236350509882</v>
+        <v>0.937569939536143</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9298077790813104</v>
+        <v>0.9350430917787204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9268133516830611</v>
+        <v>0.9382016514754986</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9268133516830611</v>
+        <v>0.9388333634148542</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.925234071834672</v>
+        <v>0.9388333634148542</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9238736350509882</v>
+        <v>0.9385175074451764</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9229260671419548</v>
+        <v>0.936361226423608</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9229260671419548</v>
+        <v>0.930991674939085</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9226102111722769</v>
+        <v>0.9295218166230486</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.919220399783413</v>
+        <v>0.9254703997834131</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9132067277321542</v>
+        <v>0.9261444138615649</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9128361609963001</v>
+        <v>0.9274078377402761</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9134678729356556</v>
+        <v>0.9251968459525314</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9039921938453208</v>
+        <v>0.9248809899828536</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9068473061998015</v>
+        <v>0.92393342207382</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9132614384983305</v>
+        <v>0.9212001398790723</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9060514619619168</v>
+        <v>0.9196208600306832</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9065737523689198</v>
+        <v>0.9209937054417472</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9045268928797039</v>
+        <v>0.9203619935023915</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9045268928797039</v>
+        <v>0.924425818969407</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8990056177240321</v>
+        <v>0.9279549454020395</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9049397617543543</v>
+        <v>0.926320954787474</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9049944725205307</v>
+        <v>0.9256892428481184</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8965881914989622</v>
+        <v>0.940850329392654</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8988414854255031</v>
+        <v>0.9405344734229762</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8988414854255031</v>
+        <v>0.9405344734229762</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8950089116505731</v>
+        <v>0.9306583340853714</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.898112760581175</v>
+        <v>0.9328693258731162</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8977969046114971</v>
+        <v>0.9357120296002166</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8988538940528833</v>
+        <v>0.9357120296002166</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9003784631350962</v>
+        <v>0.9353961736305387</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9023531269740999</v>
+        <v>0.9353961736305387</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9023531269740999</v>
+        <v>0.9353961736305387</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9023531269740999</v>
+        <v>0.9326081806696147</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9017214150347441</v>
+        <v>0.9326081806696147</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.902037271004422</v>
+        <v>0.9347644616911831</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9038776960563126</v>
+        <v>0.9344486057215053</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9032459841169569</v>
+        <v>0.9400420765273892</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9077649805974191</v>
+        <v>0.9416760671419547</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9045094079956683</v>
+        <v>0.942253068315134</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9025172592726288</v>
+        <v>0.942253068315134</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.909137826008483</v>
+        <v>0.9447799160725566</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9039498917065247</v>
+        <v>0.9450957720422344</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.879136585145745</v>
+        <v>0.9480478973016876</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8603493592636045</v>
+        <v>0.946207472249797</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8586730665102427</v>
+        <v>0.9458916162801192</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8578225115061817</v>
+        <v>0.9458916162801192</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.854044648497428</v>
+        <v>0.9443670471979063</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8659625710675931</v>
+        <v>0.9475256068946847</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8673354164786572</v>
+        <v>0.9466327497518274</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.870068698673405</v>
+        <v>0.9434741900550492</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.870068698673405</v>
+        <v>0.9436806244923743</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.870068698673405</v>
+        <v>0.9408926315314503</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8821135276599585</v>
+        <v>0.9402062088259182</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8821135276599585</v>
+        <v>0.9346426315314502</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8758088168937821</v>
+        <v>0.935480777908131</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8722920990885299</v>
+        <v>0.938748759137262</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8718544129591193</v>
+        <v>0.938748759137262</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8718544129591193</v>
+        <v>0.9224759723851638</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8699592771410523</v>
+        <v>0.9237393962638751</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8671836928075084</v>
+        <v>0.9204415215233281</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.877661650573053</v>
+        <v>0.917253068315134</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8788703636855879</v>
+        <v>0.9076081806696146</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8792285217940619</v>
+        <v>0.9069341665914629</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8771816623048462</v>
+        <v>0.9070982988899918</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8743513672051259</v>
+        <v>0.9109308726649219</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8743513672051259</v>
+        <v>0.9128260084829889</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8715086634780254</v>
+        <v>0.8992690190416027</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8800914854255031</v>
+        <v>0.8975256068946846</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8797756294558252</v>
+        <v>0.9025245916433535</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8838693484342568</v>
+        <v>0.8999430331197545</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8869731973648588</v>
+        <v>0.8975256068946846</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8530096561682159</v>
+        <v>0.8965357368468549</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8317875191769696</v>
+        <v>0.8880076256655536</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8367317931594621</v>
+        <v>0.8869506362241675</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8404549454020396</v>
+        <v>0.8863189242848118</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8310836115874018</v>
+        <v>0.8845208013717174</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8310836115874018</v>
+        <v>0.882048664380471</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8376917696958759</v>
+        <v>0.8907708013717174</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8349037767349516</v>
+        <v>0.8910866573413951</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8282832099990975</v>
+        <v>0.8911836702463676</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8269650753542099</v>
+        <v>0.8864582393285805</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8410319465752188</v>
+        <v>0.8906066690731883</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.8353166456096019</v>
+        <v>0.8762239418825015</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8356200929518997</v>
+        <v>0.8763880741810306</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8368288060644347</v>
+        <v>0.8530920043317389</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8348913681075715</v>
+        <v>0.7730039030773397</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8330086409168848</v>
+        <v>0.7764236079776194</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8154673540294197</v>
+        <v>0.7764236079776194</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8154673540294197</v>
+        <v>0.7922959344824474</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.8154673540294197</v>
+        <v>0.788244517642812</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7736248984748669</v>
+        <v>0.8157786977709593</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7736248984748669</v>
+        <v>0.8177285443552026</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7688994675570797</v>
+        <v>0.8142541286887466</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.8242069759047017</v>
+        <v>0.8237597012904972</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.8083171645158379</v>
+        <v>0.7831535962458263</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6119246909123726</v>
+        <v>0.783469452215504</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5997828490208464</v>
+        <v>0.7413111406912734</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5903145023012364</v>
+        <v>0.7324970670517101</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.611521410522516</v>
+        <v>0.7329223445537406</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5877526847757423</v>
+        <v>0.733305319916975</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5623945266672683</v>
+        <v>0.7078727100442198</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5608947748398159</v>
+        <v>0.7101683061095569</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5410607120296003</v>
+        <v>0.6941639969316848</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.555053131486328</v>
+        <v>0.6860662395090695</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5788320097464128</v>
+        <v>0.6720467466835123</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5749373928345817</v>
+        <v>0.6314553063802906</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6016706524681887</v>
+        <v>0.6460743615197184</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5882580543272268</v>
+        <v>0.6654137713202779</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5594604503203682</v>
+        <v>0.6417916929879974</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5397132479018139</v>
+        <v>0.6442514213518635</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5359652784044762</v>
+        <v>0.6486361790452125</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5275888908943236</v>
+        <v>0.6368524952621605</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5249526216045484</v>
+        <v>0.6387476310802275</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5249526216045484</v>
+        <v>0.6260084829888999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5170562223626026</v>
+        <v>0.5896997112173992</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5205306380290587</v>
+        <v>0.5739390623589928</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.525584333543904</v>
+        <v>0.616962593628734</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5262160454832596</v>
+        <v>0.5900849426947026</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5249526216045484</v>
+        <v>0.5565889811388864</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5388502842703727</v>
+        <v>0.5541241765183648</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5379574271275156</v>
+        <v>0.5532313193755076</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5323391390668712</v>
+        <v>0.5508770643443732</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5157504963450952</v>
+        <v>0.5275110549589387</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5275465887555275</v>
+        <v>0.5275110549589387</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5288647234004151</v>
+        <v>0.5113674307372981</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5268725746773757</v>
+        <v>0.5422840898835845</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5268725746773757</v>
+        <v>0.5679507715910117</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5179738967602202</v>
+        <v>0.5580746322534067</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5188667539030773</v>
+        <v>0.5577587762837288</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5194561637036369</v>
+        <v>0.5577587762837288</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.520349020846494</v>
+        <v>0.5628051394278495</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.520349020846494</v>
+        <v>0.5100741133471709</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5182722678458622</v>
+        <v>0.5100741133471709</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5150465887555274</v>
+        <v>0.485116415485967</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5082246638390037</v>
+        <v>0.4801298393646782</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5088563757783594</v>
+        <v>0.5159766717805252</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5098039436873929</v>
+        <v>0.5166083837198809</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5098039436873929</v>
+        <v>0.5133578873747857</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5045861158740186</v>
+        <v>0.5133578873747857</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5043249706705171</v>
+        <v>0.49921148813284</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5023751240862738</v>
+        <v>0.5004749120115514</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.5004749120115514</v>
       </c>
     </row>
   </sheetData>
